--- a/WorkBot/main/data/order_archive/Albert's Organics/Albert's Organics_Bakery_20260516.xlsx
+++ b/WorkBot/main/data/order_archive/Albert's Organics/Albert's Organics_Bakery_20260516.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,90 +731,6 @@
         <v>33.54</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>97920</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Natalie's - Honey Tangerine</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>12.16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>97928</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Natalie's - Lemonade</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>97929</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Natalie's - Strawberry Lemonade</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="E20" t="n">
-        <v>49.86</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>49042</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Harney &amp; Sons - Green with Coconut</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="E21" t="n">
-        <v>18.18</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
